--- a/Project/Slots/其他/Game List_Online.xlsx
+++ b/Project/Slots/其他/Game List_Online.xlsx
@@ -3435,10 +3435,11 @@
         <v>0.02</v>
       </c>
       <c r="S38" s="39">
-        <v>0.94</v>
+        <v>0.9399</v>
       </c>
       <c r="T38" s="39">
-        <v>0.96</v>
+        <f>S38+R38</f>
+        <v>0.9599</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
